--- a/example_files/west_nile_metadata.xlsx
+++ b/example_files/west_nile_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mverbies/projects/example_data/example_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50734963-929A-6649-B5A8-284047D79543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCCFA75-3FF4-874F-9430-AABE04615A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{8AA6C4E1-612A-6248-8120-629076D7CFF1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>submissionId</t>
   </si>
@@ -288,6 +288,18 @@
   </si>
   <si>
     <t>host</t>
+  </si>
+  <si>
+    <t>sequencingInstrument</t>
+  </si>
+  <si>
+    <t>Illumina HiSeq 1000</t>
+  </si>
+  <si>
+    <t>raw_reads_1.fq.gz</t>
+  </si>
+  <si>
+    <t>files.rawReads</t>
   </si>
 </sst>
 </file>
@@ -1149,14 +1161,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC5AC95-285D-7643-A533-C3A9B14982C8}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
     <col min="11" max="11" width="27" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1196,8 +1210,14 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
+      <c r="N1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1225,8 +1245,14 @@
       <c r="M2" s="1">
         <v>40742</v>
       </c>
+      <c r="N2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1264,7 +1290,7 @@
         <v>40367</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1302,7 +1328,7 @@
         <v>42548</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1340,7 +1366,7 @@
         <v>41506</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1378,7 +1404,7 @@
         <v>42933</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1416,7 +1442,7 @@
         <v>41943</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1454,7 +1480,7 @@
         <v>39709</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1489,7 +1515,7 @@
         <v>37892</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1553,7 @@
         <v>40402</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1565,7 +1591,7 @@
         <v>42201</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>76</v>
       </c>
